--- a/far_creation/far.xlsx
+++ b/far_creation/far.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,56 +436,127 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LB IP</t>
+          <t>Node Info</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VIP1 1.1.1.1 
- VIP2 2.2.2.2</t>
+          <t xml:space="preserve"> Bastion/Registry 1.1.1.1
+ Bootstrap 2.2.2.2
+ Master 1 3.3.3.3
+ Master 2 4.4.4.4
+ Worker string
+ Central Bastion 10.177.111.65
+ Central Mirror 10.177.111.66
+</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vip1 and Vip2</t>
+          <t>Node Ip info</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LDAP url</t>
+          <t>LB IP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ldap-url</t>
+          <t>VIP1: string_vip1
+VIP2: string_vip2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LDAP url</t>
+          <t>VIP info</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Node Info</t>
+          <t>LDAP url</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bastion Nodes: string 
- Bootstrap Nodes: 3.3.3.3, 4.4.4.4 
- Master Nodes: string 
- Worker Nodes: string 
- Infra Nodes: string</t>
+          <t>ldap://something</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Node Ip info</t>
+          <t>This url is used to establish connection between Ocp cluster and vcenter platform as well as authentication</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LDAP IP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>corp.ad.sbi
+10.189.37.135
+10.189.37.136
+10.189.37.137
+10.176.54.30
+10.176.54.31
+10.176.54.32
+10.176.53.145</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Used for authentication</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NTP IP</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>10.191.174.52
+10.191.174.53
+10.179.70.2
+10.179.70.3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Used for time sync</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Windows IP</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>10.0.70.28
+10.0.88.137
+10.0.70.26
+10.0.70.17
+10.0.70.239
+10.0.70.23
+10.0.88.148
+10.0.88.151</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Meghdoot OCP Team's desktop IP</t>
         </is>
       </c>
     </row>

--- a/far_creation/far.xlsx
+++ b/far_creation/far.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="LB_Details" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -42,12 +46,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,90 +454,96 @@
   </sheetPr>
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="174" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Host-Description</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Host-Ips</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Details</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Node Info</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> Bastion/Registry 1.1.1.1
  Bootstrap 2.2.2.2
  Master 1 3.3.3.3
  Master 2 4.4.4.4
  Worker string
+ Infra string
  Central Bastion 10.177.111.65
  Central Mirror 10.177.111.66
 </t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Node Ip info</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>LB IP</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>VIP1: string_vip1
 VIP2: string_vip2</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>VIP info</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>LDAP url</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>ldap://something</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>This url is used to establish connection between Ocp cluster and vcenter platform as well as authentication</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>LDAP IP</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>corp.ad.sbi
 10.189.37.135
@@ -510,19 +555,19 @@
 10.176.53.145</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Used for authentication</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>NTP IP</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>10.191.174.52
 10.191.174.53
@@ -530,19 +575,19 @@
 10.179.70.3</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Used for time sync</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Windows IP</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>10.0.70.28
 10.0.88.137
@@ -554,7 +599,7 @@
 10.0.88.151</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Meghdoot OCP Team's desktop IP</t>
         </is>
@@ -563,4 +608,188 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FrontEnd</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FrontEndPort</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>BackendPort</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>api.produat.bank.sbi</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>6443</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>bootstrap.produat.bank.sbi</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>6443</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>6443</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>master.produat.bank.sbi</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>6443</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>6443</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>master.produat.bank.sbi</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6443</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>api-int.produat.bank.sbi</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>22623</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>bootstrap.produat.bank.sbi</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22623</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>22623</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>master.produat.bank.sbi</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22623</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>22623</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>master.produat.bank.sbi</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22623</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>*.apps.produat.bank.sbi</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>infra.produat.bank.sbi</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>